--- a/output/pdf_financials_xlsx/COO.xlsx
+++ b/output/pdf_financials_xlsx/COO.xlsx
@@ -5223,46 +5223,46 @@
         <v>1.397668</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>1.678768</v>
+        <v>1.441452</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.709025</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.955774</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.262353</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.430875</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.468208</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.490743</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.699081</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.699081</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.699081</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.838622</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.954513</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>3.187261</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>3.295657</v>
       </c>
     </row>
     <row r="93">
@@ -9471,7 +9471,11 @@
           <t>Reserves 16</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -11138,7 +11142,11 @@
           <t>Reserves 14</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -12054,7 +12062,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -13395,7 +13407,11 @@
           <t>Reserves 17</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -14186,7 +14202,11 @@
           <t>Reserves 18</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -15513,7 +15533,11 @@
           <t>Share-based payment reserve 18</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -16047,7 +16071,11 @@
           <t>Share-based payment reserve 17</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -17412,7 +17440,11 @@
           <t>Share-based payment reserve 19</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -20603,7 +20635,11 @@
           <t>Share-based payment reserve 1,709,025</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/COO.xlsx
+++ b/output/pdf_financials_xlsx/COO.xlsx
@@ -969,49 +969,49 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.015654</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.02804</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.019443</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.003576</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.002452</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000179</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.04297</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.054263</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.000153</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.000158</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.03765</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.00222</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.00267</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.002081</v>
       </c>
     </row>
     <row r="13">
@@ -1827,49 +1827,49 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.440662</v>
+        <v>-1.456316</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.462395</v>
+        <v>-2.490435</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.412838</v>
+        <v>-2.432281</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.123386</v>
+        <v>0.11981</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.296606</v>
+        <v>-3.299058</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.914629</v>
+        <v>-1.914808</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.255675</v>
+        <v>-2.298645</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.914107</v>
+        <v>-1.96837</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>0.352178</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.749895</v>
+        <v>0.749742</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.583812</v>
+        <v>0.583654</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.490351</v>
+        <v>-0.5280010000000001</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-1.823325</v>
+        <v>-1.825545</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-4.579652</v>
+        <v>-4.582322</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>1.59251</v>
+        <v>1.590429</v>
       </c>
     </row>
     <row r="28">
@@ -1931,49 +1931,49 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.440662</v>
+        <v>-1.456316</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.44937</v>
+        <v>-2.47741</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.382095</v>
+        <v>-2.401538</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.127386</v>
+        <v>0.12381</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.245206</v>
+        <v>-3.247658</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.859429</v>
+        <v>-1.859608</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.175475</v>
+        <v>-2.218445</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.799128</v>
+        <v>-1.853391</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>0.434918</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.774895</v>
+        <v>0.774742</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.608812</v>
+        <v>0.608654</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.490351</v>
+        <v>-0.5280010000000001</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.823325</v>
+        <v>-1.825545</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-4.579652</v>
+        <v>-4.582322</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1.59251</v>
+        <v>1.590429</v>
       </c>
     </row>
     <row r="30">
@@ -1983,49 +1983,49 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-48.37621279513559</v>
+        <v>-48.90186088961927</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-90.85705807073836</v>
+        <v>-91.89717528794257</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-39.92537169591757</v>
+        <v>-40.25124828853194</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>3.834219504596904</v>
+        <v>3.726584686418779</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-45.73736495649377</v>
+        <v>-45.77192301501866</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-35.30608094752646</v>
+        <v>-35.3094797266622</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-59.33575915869081</v>
+        <v>-60.50775955908565</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-48.9951133642842</v>
+        <v>-50.47284137278952</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>20.25569839679685</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>28.12212389637462</v>
+        <v>28.11657129253004</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>21.35606966263126</v>
+        <v>21.35052729650396</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-12.36819643385027</v>
+        <v>-13.31784800126721</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-39.60665846725441</v>
+        <v>-39.65488178553135</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-132.2524388423163</v>
+        <v>-132.3295438301426</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>6.178851265449892</v>
+        <v>6.170777099834982</v>
       </c>
     </row>
     <row r="31">
@@ -2146,49 +2146,49 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.792733</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.792733</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.573531</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.810736</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.73219</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.834972</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.188116</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.4045</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.529995</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.509725</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.565925</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.9779099999999999</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.347522</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.55071</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>1.718815</v>
       </c>
     </row>
     <row r="35">
@@ -2250,49 +2250,49 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.792733</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.792733</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.573531</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.810736</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.73219</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.834972</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.188116</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.4045</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.529995</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.509725</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.565925</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.9779099999999999</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.347522</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.55071</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>1.718815</v>
       </c>
     </row>
     <row r="37">
@@ -2874,49 +2874,49 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.845905</v>
+        <v>0.053172</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.845905</v>
+        <v>0.053172</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.697509</v>
+        <v>0.123978</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.052428</v>
+        <v>0.241692</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.827555</v>
+        <v>1.095365</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.473294</v>
+        <v>0.6383219999999999</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.08263</v>
+        <v>0.894514</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.68369</v>
+        <v>0.27919</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.760081</v>
+        <v>0.230086</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>2.496509</v>
+        <v>1.986784</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.840287</v>
+        <v>0.274362</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.433612</v>
+        <v>0.455702</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.71124</v>
+        <v>0.363718</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.785246</v>
+        <v>0.234536</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>2.007092</v>
+        <v>0.288277</v>
       </c>
     </row>
     <row r="49">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -18979,7 +18979,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -44148,7 +44148,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -44241,7 +44241,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -46834,7 +46834,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -53648,7 +53648,7 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
@@ -62650,7 +62650,7 @@
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
@@ -62745,7 +62745,7 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
@@ -67716,7 +67716,7 @@
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
@@ -71532,7 +71532,7 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E715" s="5" t="n">

--- a/output/pdf_financials_xlsx/COO.xlsx
+++ b/output/pdf_financials_xlsx/COO.xlsx
@@ -1903,7 +1903,7 @@
         <v>0.114979</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.08273999999999999</v>
+        <v>0.025</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>0.025</v>
@@ -1955,7 +1955,7 @@
         <v>-1.853391</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.434918</v>
+        <v>0.377178</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>0.774742</v>
@@ -2007,7 +2007,7 @@
         <v>-50.47284137278952</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>20.25569839679685</v>
+        <v>17.56653854268401</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>28.11657129253004</v>
@@ -5609,19 +5609,19 @@
         <v>0</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.114979</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.08273999999999999</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="M100" s="3" t="n">
         <v>0</v>
@@ -6227,16 +6227,16 @@
         <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.00405</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.017191</v>
       </c>
       <c r="H112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.003566</v>
       </c>
       <c r="J112" s="3" t="n">
         <v>0</v>
@@ -6245,7 +6245,7 @@
         <v>0</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.007936</v>
       </c>
       <c r="M112" s="3" t="n">
         <v>0</v>
@@ -26873,7 +26873,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -26958,7 +26958,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -50343,7 +50347,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
@@ -52942,7 +52946,7 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
@@ -55351,7 +55355,7 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
@@ -61293,7 +61297,7 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">

--- a/output/pdf_financials_xlsx/COO.xlsx
+++ b/output/pdf_financials_xlsx/COO.xlsx
@@ -1453,11 +1453,13 @@
       <c r="D20" s="3" t="n">
         <v>-2.412838</v>
       </c>
-      <c r="E20" s="3" t="n">
-        <v>0.772375</v>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-0.126014</v>
+        <v>-3.170592</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>-1.914629</v>
@@ -1506,10 +1508,10 @@
         <v>0</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0</v>
+        <v>0.772375</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0</v>
+        <v>-0.126014</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>0</v>
@@ -1521,10 +1523,10 @@
         <v>0</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0</v>
+        <v>0.191288</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
+        <v>0.368659</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>0</v>
@@ -2464,43 +2466,43 @@
         <v>0.032761</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.009486</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.007767</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.001965</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.000175</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.09063400000000001</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.029174</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.088043</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>0.003256</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>0.007941</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>0.019158</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>0.124621</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>0.034685</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>0.018752</v>
       </c>
     </row>
     <row r="41">
@@ -2543,16 +2545,16 @@
         <v>0.129357</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>0.2031</v>
+        <v>0.222258</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>0.456011</v>
+        <v>0.580632</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>0.255667</v>
+        <v>0.290352</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0.187059</v>
+        <v>0.205811</v>
       </c>
     </row>
     <row r="42">
@@ -2907,16 +2909,16 @@
         <v>0.274362</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.455702</v>
+        <v>0.436544</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.363718</v>
+        <v>0.239097</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.234536</v>
+        <v>0.199851</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.288277</v>
+        <v>0.269525</v>
       </c>
     </row>
     <row r="49">
@@ -3898,43 +3900,43 @@
         <v>0.333978</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.078988</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.291894</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.301386</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.192544</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.288924</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.693678</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.602621</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.35043</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.328252</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.33798</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.719839</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.495238</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.5655</v>
       </c>
     </row>
     <row r="68">
@@ -5912,40 +5914,40 @@
         <v>0.467481</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.421493</v>
+        <v>0.341711</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>-1.601666</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.4</v>
+        <v>0.131362</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0</v>
+        <v>-0.433005</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0</v>
+        <v>0.749229</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0</v>
+        <v>-0.08777</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0</v>
+        <v>-0.243154</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0</v>
+        <v>-0.088063</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0</v>
+        <v>-1.089116</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0</v>
+        <v>0.810258</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0</v>
+        <v>2.679401</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>0</v>
+        <v>0.7653180000000001</v>
       </c>
     </row>
     <row r="107">
@@ -6123,19 +6125,19 @@
         <v>0</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.311055</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.299082</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.08677700000000001</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.022727</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.022727</v>
       </c>
       <c r="K110" s="3" t="n">
         <v>0</v>
@@ -6178,10 +6180,10 @@
         <v>-0.039202</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>0.005386</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.010081</v>
       </c>
       <c r="I111" s="3" t="n">
         <v>-0.01592</v>
@@ -7404,10 +7406,10 @@
         <v>-0.039202</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.005386</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.010081</v>
       </c>
       <c r="I134" s="3" t="n">
         <v>-0.01592</v>
@@ -7456,10 +7458,10 @@
         <v>-0.308412</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>0.176339</v>
+        <v>0.170953</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-1.176384</v>
+        <v>-1.186465</v>
       </c>
       <c r="I135" s="3" t="n">
         <v>-0.151091</v>
@@ -23618,7 +23620,11 @@
           <t>Changes in non-cash operating working capital (Note 25):</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -25360,7 +25366,11 @@
           <t>Changes in non-cash operating working capital (Note 22):</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -25718,7 +25728,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
@@ -26341,7 +26355,11 @@
           <t>Changes in non-cash operating working capital (Note 21):</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>
@@ -26430,7 +26448,11 @@
           <t>Net proceeds from private placement</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -27411,7 +27433,11 @@
           <t>Changes in non-cash operating working capital (note 25):</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -29474,7 +29500,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -30469,7 +30499,11 @@
           <t>Changes in non-cash operating working capital (note 26):</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
           <t>-</t>
@@ -31994,7 +32028,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -34223,7 +34261,11 @@
           <t>Changes in non-cash operating working capital (note 26):</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -34312,7 +34354,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr">
         <is>
           <t>-</t>
@@ -35730,7 +35776,11 @@
           <t>Changes in non-cash operating working capital (note 27):</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -35819,7 +35869,11 @@
           <t>Disposition (acquisition) of equipment</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
           <t>-</t>
@@ -36361,7 +36415,11 @@
           <t>Changes in non-cash operating working capital: (note 26)</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
@@ -37435,7 +37493,11 @@
           <t>Changes in non-cash operating working capital: (note 28)</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E336" t="inlineStr">
         <is>
           <t>-</t>
@@ -53925,7 +53987,11 @@
           <t>Income from discontinued operations 5</t>
         </is>
       </c>
-      <c r="D520" t="inlineStr"/>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E520" t="inlineStr">
         <is>
           <t>-</t>
@@ -63105,7 +63171,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D622" t="inlineStr"/>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E622" t="inlineStr">
         <is>
           <t>-</t>
@@ -63194,7 +63264,11 @@
           <t>Loss from discontinued operations 10</t>
         </is>
       </c>
-      <c r="D623" t="inlineStr"/>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E623" t="inlineStr">
         <is>
           <t>-</t>
@@ -66351,7 +66425,7 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>NetIncomeContinuousOperations</t>
+          <t>NetIncomeDiscontinuousOperations</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
